--- a/data/lanchonete.xlsx
+++ b/data/lanchonete.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Clientes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fornecedores" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Filiais" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pedidos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ItensPedido" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Configuracoes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BoardItens" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clientes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fornecedores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filiais" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItensPedido" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracoes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$I$4</definedName>
@@ -22,7 +21,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fornecedores'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Filiais'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Configuracoes'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BoardItens'!$A$1:$Q$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,28 +488,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>X-Salada</t>
+          <t>Batata frita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pão, hambúrguer, queijo, alface e tomate.</t>
+          <t>Porção individual de batata frita.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lanches</t>
+          <t>Acompanhamentos</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18.9</v>
+        <v>9.5</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -522,28 +520,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Batata frita</t>
+          <t>Refrigerante lata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Porção individual de batata frita.</t>
+          <t>Lata de 350 ml.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Acompanhamentos</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -554,34 +552,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Refrigerante lata</t>
+          <t>dcsdcs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lata de 350 ml.</t>
+          <t>dcsdc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bebidas</t>
+          <t>sdcsd</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>45.88</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:56</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1016,6 +1019,11 @@
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1059,7 +1067,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1093,7 +1101,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1106,277 +1114,4 @@
   <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>titulo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>descricao</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>origem</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>github_item_id</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>github_project_id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>github_item_type</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>github_issue_number</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>github_repository</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>github_url</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>github_status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>github_status_field_id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>github_status_option_id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ativo</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>criado_em</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>atualizado_em</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AC1 — Produtos</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cadastro, alteração, exclusão e visualização dos produtos.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CONCLUIDO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LOCAL</t>
-        </is>
-      </c>
-      <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:37</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AC2 — Clientes</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Cadastro, alteração, exclusão e visualização dos clientes.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CONCLUIDO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LOCAL</t>
-        </is>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:37</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AC3 — Fornecedores</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cadastro, alteração, exclusão e visualização dos fornecedores.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CONCLUIDO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LOCAL</t>
-        </is>
-      </c>
-      <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:37</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Prova final — Filiais e pedidos</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Concluir o fluxo de filiais, pedidos, estoque e apresentação.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>EM_PROGRESSO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LOCAL</t>
-        </is>
-      </c>
-      <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:37</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:37</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:Q5"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/lanchonete.xlsx
+++ b/data/lanchonete.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clientes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fornecedores" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filiais" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItensPedido" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracoes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Produtos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Clientes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fornecedores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Filiais" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pedidos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ItensPedido" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Configuracoes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$I$4</definedName>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/data/lanchonete.xlsx
+++ b/data/lanchonete.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Configuracoes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produtos'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clientes'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fornecedores'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Filiais'!$A$1:$I$2</definedName>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -550,45 +550,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>dcsdcs</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>dcsdc</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>sdcsd</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="F4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-09-14T07:56</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1067,7 +1030,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1084,7 +1047,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1101,7 +1064,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
